--- a/sources/eddy_step6b.xlsx
+++ b/sources/eddy_step6b.xlsx
@@ -417,24 +417,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T186"/>
+  <dimension ref="A1:T191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="51" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
-    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="49" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
     <col width="32" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
     <col width="14" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="123" customWidth="1" min="15" max="15"/>
+    <col width="122" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
     <col width="38" customWidth="1" min="17" max="17"/>
     <col width="38" customWidth="1" min="18" max="18"/>
@@ -2822,7 +2822,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>f+1+2 [~db]</t>
+          <t>f+1+2 [~B]</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3298,12 +3298,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>f,f+3 [~B] [~D]</t>
+          <t>f,f+3</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Lunging Brush Fire [HSP ][RLX]</t>
+          <t>Lunging Brush Fire</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>(~B)HSP; (~D)RLX</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3355,17 +3360,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>df+3 [~D]</t>
+          <t>df+3</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Island Mirage [RLX]</t>
+          <t>Island Mirage</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>HSP</t>
+          <t>HSP; (~D)RLX</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -3474,12 +3479,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>db+3 [~B]</t>
+          <t>db+3</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Weed Whacker [HSP]</t>
+          <t>Weed Whacker</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -3878,12 +3888,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>– ~4 [~B]</t>
+          <t>– ~4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>– Shin Cutter [HSP]</t>
+          <t>– Shin Cutter</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -3940,12 +3955,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>–– 4 [~B]</t>
+          <t>–– 4</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>–– Cross Cutter [HSP]</t>
+          <t>–– Cross Cutter</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4168,17 +4188,22 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>u+3+4 [~D_~B]</t>
+          <t>u+3+4</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>uf+3+4 [~D_~B]</t>
+          <t>uf+3+4</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Fire Kick [RLX]</t>
+          <t>Fire Kick</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>(~D)RLX; (~B)RLX</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4230,12 +4255,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>3+4 [~B]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Back Handstand Spring [HSP]</t>
+          <t>Back Handstand Spring</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4292,17 +4322,22 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>FC+3+4 [~B] [~D]</t>
+          <t>FC+3+4</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>WS+3+4 [~B] [~D]</t>
+          <t>WS+3+4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Front Stinger [HSP] [RLX]</t>
+          <t>Front Stinger</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>(~B)HSP; (~D)RLX</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -4498,17 +4533,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3~4 [~B]</t>
+          <t>3~4</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Slippery Kick Series [HSP]</t>
+          <t>Slippery Kick Series</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>RLX</t>
+          <t>RLX; (~B)HSP</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -4565,12 +4600,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>– 4 [~B]</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>– Slider [HSP]</t>
+          <t>– Slider</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -4627,12 +4667,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>– 4,4 [~B]</t>
+          <t>– 4,4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>– Slide Flop [HSP]</t>
+          <t>– Slide Flop</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -4974,12 +5019,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>f+4 [~B]</t>
+          <t>f+4</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Samba [HSP]</t>
+          <t>Samba</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5331,12 +5381,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>– 3 [~B]</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>– Weed Whacker [HSP]</t>
+          <t>– Weed Whacker</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -5611,7 +5666,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>–– 4 [~B]</t>
+          <t>–– 4</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -5730,12 +5785,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>–– ~4 [~B]</t>
+          <t>–– ~4</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>–– Shin Cutter [HSP]</t>
+          <t>–– Shin Cutter</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -5958,12 +6018,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>––– 4 [~B]</t>
+          <t>––– 4</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>––– Cross Cutter [HSP]</t>
+          <t>––– Cross Cutter</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -6015,12 +6080,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>– 4 [~D]</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>– Mars Attacks [RLX]</t>
+          <t>– Mars Attacks</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>(~D)RLX</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -6129,52 +6199,47 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>db+4,4,4,4,... [b+4]</t>
+          <t>db+4</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Barbed Wire [HSP]</t>
+          <t>Barbed Wire</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>17 x</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>-12 -7 -7 -7...-17</t>
+          <t>-12</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>KD KD KD KD...-1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>KD KD KD KD...-1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>15,30,30,30...12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>15,30,30,30...12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>hhhh...m</t>
-        </is>
-      </c>
-      <c r="O104" t="inlineStr">
-        <is>
-          <t>Can be continued infinitely.</t>
+          <t>h</t>
         </is>
       </c>
       <c r="Q104" t="inlineStr">
@@ -6191,223 +6256,228 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>u+4</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>uf+4</t>
+          <t>db+4,b+4</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Roundhouse</t>
+          <t>Barbed Wire</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>HSP</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-12 -17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD -1</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD -1</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>15,12</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>hm</t>
         </is>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
-          <t>8914f23d-a49e-49d4-a78b-345e8134c95a</t>
+          <t>4f07880c-ce7b-476f-a3fa-8dd3dc28476c</t>
         </is>
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>a7747524-95e6-4e43-a857-96514478bfce</t>
+          <t>84fbd428-9800-49bd-8ba0-d56663d712bc</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>4~3</t>
+          <t>db+4,4(repeat)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Satellite Moon</t>
+          <t>Barbed Wire</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>-108</t>
+          <t>-12 -7</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>-104</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>-104</t>
+          <t>KD KD</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>16,20</t>
+          <t>15,30</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>mh</t>
+          <t>hh</t>
         </is>
       </c>
       <c r="Q106" t="inlineStr">
         <is>
-          <t>ea4e96d7-dbbf-4189-aa7f-54bb2ba314aa</t>
+          <t>5dfafb7e-bc6e-4aa5-be9d-cf4cd62598d3</t>
         </is>
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>644152ee-8d17-421d-8487-b0b6a8e59c77</t>
+          <t>84fbd428-9800-49bd-8ba0-d56663d712bc</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>– 3 [~B]</t>
+          <t>db+4,4(repeat),b+4</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>– Hot Plate [HSP]</t>
+          <t>Barbed Wire</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>RLX</t>
+          <t>HSP</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>17</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>-12 -7 -17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>KD KD -1</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>KD KD -1</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>15,30,12</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>57</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>hhm</t>
         </is>
       </c>
       <c r="Q107" t="inlineStr">
         <is>
-          <t>a70b9e10-88a1-4a3b-8a3f-6c4d62484351</t>
+          <t>7e9692bb-f6f0-44b7-9a34-37045ad20f25</t>
         </is>
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>4939c92c-6e15-4eab-8894-f14fc71d4718</t>
-        </is>
-      </c>
-      <c r="S107" t="inlineStr">
-        <is>
-          <t>ea4e96d7-dbbf-4189-aa7f-54bb2ba314aa</t>
+          <t>84fbd428-9800-49bd-8ba0-d56663d712bc</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>D,db+4</t>
+          <t>u+4</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>uf+4</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Haule</t>
+          <t>Roundhouse</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>-10</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>+1</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -6417,371 +6487,421 @@
       </c>
       <c r="Q108" t="inlineStr">
         <is>
-          <t>b28f0455-bb63-4a5d-baa8-dd8450cf34fe</t>
+          <t>8914f23d-a49e-49d4-a78b-345e8134c95a</t>
         </is>
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>b10cfea2-6cca-4098-b743-3164e76ae9e2</t>
+          <t>a7747524-95e6-4e43-a857-96514478bfce</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>u,ub</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Evasive Back Flip</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>HSP</t>
+          <t>Satellite Moon</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>-108</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>-104</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>-104</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>16,20</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>mh</t>
         </is>
       </c>
       <c r="Q109" t="inlineStr">
         <is>
-          <t>65b0f41b-9d74-45ef-aa0d-f709601122e6</t>
+          <t>ea4e96d7-dbbf-4189-aa7f-54bb2ba314aa</t>
         </is>
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>a8bf87ae-c064-467c-81e9-46f441fb26c7</t>
+          <t>644152ee-8d17-421d-8487-b0b6a8e59c77</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>– 3 [~B]</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>– Hot Plate [HSP]</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>RLX</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>a70b9e10-88a1-4a3b-8a3f-6c4d62484351</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>4939c92c-6e15-4eab-8894-f14fc71d4718</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>ea4e96d7-dbbf-4189-aa7f-54bb2ba314aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>D,db+4</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Haule</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>-10</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>+1</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>b28f0455-bb63-4a5d-baa8-dd8450cf34fe</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>b10cfea2-6cca-4098-b743-3164e76ae9e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>u,ub</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Evasive Back Flip</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>HSP</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>65b0f41b-9d74-45ef-aa0d-f709601122e6</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>a8bf87ae-c064-467c-81e9-46f441fb26c7</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>d+1+2; SS</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>Rewinder</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="Q110" t="inlineStr">
+      <c r="Q113" t="inlineStr">
         <is>
           <t>33619bbd-ea93-4026-8169-7a0deaf141bd</t>
         </is>
       </c>
-      <c r="R110" t="inlineStr">
+      <c r="R113" t="inlineStr">
         <is>
           <t>15ffbab3-d680-435e-b17c-73d9d90e6922</t>
         </is>
       </c>
     </row>
-    <row r="111"/>
-    <row r="112">
-      <c r="A112" s="1" t="inlineStr">
+    <row r="114"/>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
         <is>
           <t>Handstand Position Arts</t>
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="1" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
+      <c r="B116" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="C113" s="1" t="inlineStr">
+      <c r="C116" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="D113" s="1" t="inlineStr">
+      <c r="D116" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="E113" s="1" t="inlineStr">
+      <c r="E116" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="F113" s="1" t="inlineStr">
+      <c r="F116" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="G113" s="1" t="inlineStr">
+      <c r="G116" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="H113" s="1" t="inlineStr">
+      <c r="H116" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="I113" s="1" t="inlineStr">
+      <c r="I116" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="J113" s="1" t="inlineStr">
+      <c r="J116" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="K113" s="1" t="inlineStr">
+      <c r="K116" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="L113" s="1" t="inlineStr">
+      <c r="L116" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="M113" s="1" t="inlineStr">
+      <c r="M116" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="N113" s="1" t="inlineStr">
+      <c r="N116" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="O113" s="1" t="inlineStr">
+      <c r="O116" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="P113" s="1" t="inlineStr">
+      <c r="P116" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Q113" s="1" t="inlineStr">
+      <c r="Q116" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="R113" s="1" t="inlineStr">
+      <c r="R116" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="S113" s="1" t="inlineStr">
+      <c r="S116" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="T113" s="1" t="inlineStr">
+      <c r="T116" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Moves starting from Handstand Position only - HSP</t>
-        </is>
-      </c>
-      <c r="Q114" t="inlineStr">
-        <is>
-          <t>5f6a2960-0771-413b-9f0b-e8c481e60a9f</t>
-        </is>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>be647f57-edc9-4709-bf29-e5bb34984d6e</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>u</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>d</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Handstand Sidestep</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>HSP</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q115" t="inlineStr">
-        <is>
-          <t>23a86858-a5af-4061-b595-c048ffa5e0ea</t>
-        </is>
-      </c>
-      <c r="R115" t="inlineStr">
-        <is>
-          <t>815fb48d-4f62-47b3-834b-bcb1f673014d</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Handstand Walk</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>HSP</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>d19752d4-1385-4f51-a7fd-b53e1a82a2d6</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>75c0556a-eea6-4411-9be7-f9d69ad86c11</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Handstand Perch</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>HSP</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>Moves starting from Handstand Position only - HSP</t>
         </is>
       </c>
       <c r="Q117" t="inlineStr">
         <is>
-          <t>ddeb97e3-408e-431d-a376-653d303a8e74</t>
+          <t>5f6a2960-0771-413b-9f0b-e8c481e60a9f</t>
         </is>
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>51b8771e-4dc8-4299-9d70-8b8f171a6119</t>
+          <t>be647f57-edc9-4709-bf29-e5bb34984d6e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>u</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Stand Up</t>
+          <t>Handstand Sidestep</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>HSP</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -6801,29 +6921,29 @@
       </c>
       <c r="Q118" t="inlineStr">
         <is>
-          <t>d5072ac8-5b2c-4238-af93-2be6fed6e850</t>
+          <t>23a86858-a5af-4061-b595-c048ffa5e0ea</t>
         </is>
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2c4e3e13-6c58-4f15-91d8-ce7e531fc26c</t>
+          <t>815fb48d-4f62-47b3-834b-bcb1f673014d</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Handstand Roll</t>
+          <t>Handstand Walk</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>RLX</t>
+          <t>HSP</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -6843,24 +6963,24 @@
       </c>
       <c r="Q119" t="inlineStr">
         <is>
-          <t>ea8439e5-4984-41a7-ab55-81ecc867c1cd</t>
+          <t>d19752d4-1385-4f51-a7fd-b53e1a82a2d6</t>
         </is>
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>f73f5c3d-92a7-4c62-9805-43c4cc206747</t>
+          <t>75c0556a-eea6-4411-9be7-f9d69ad86c11</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>F+1+2</t>
+          <t>D</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Tuck &amp; Roll</t>
+          <t>Handstand Perch</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -6885,614 +7005,574 @@
       </c>
       <c r="Q120" t="inlineStr">
         <is>
-          <t>c2d21e2d-66e0-46d4-9733-c8f936ca3d82</t>
+          <t>ddeb97e3-408e-431d-a376-653d303a8e74</t>
         </is>
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>fc7b77a4-f1c5-4ea8-a313-46e23e625a23</t>
+          <t>51b8771e-4dc8-4299-9d70-8b8f171a6119</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>b</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>N</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Left Flop Punch</t>
-        </is>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>+9</t>
+          <t>Stand Up</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N121" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="O121" t="inlineStr">
-        <is>
-          <t>Continue with the Leg Whip Strings.</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q121" t="inlineStr">
         <is>
-          <t>511c5803-e5cd-47d4-8b8a-4da8499f5ec6</t>
+          <t>d5072ac8-5b2c-4238-af93-2be6fed6e850</t>
         </is>
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2c914bd9-7ae6-48cc-8c08-e4722a912cf2</t>
+          <t>2c4e3e13-6c58-4f15-91d8-ce7e531fc26c</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Right Flop Punch</t>
-        </is>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>+9</t>
-        </is>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>+9</t>
+          <t>Handstand Roll</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>RLX</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N122" t="inlineStr">
-        <is>
-          <t>RC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q122" t="inlineStr">
         <is>
-          <t>4510911a-6378-49ee-b18f-8b95ee7d73e1</t>
+          <t>ea8439e5-4984-41a7-ab55-81ecc867c1cd</t>
         </is>
       </c>
       <c r="R122" t="inlineStr">
         <is>
-          <t>4b07173b-e8f3-4dc6-824a-6b3b6476e46c</t>
+          <t>f73f5c3d-92a7-4c62-9805-43c4cc206747</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>– 4 - [~B]</t>
+          <t>F+1+2</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>– Swirl Kick [HSP]</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>-5</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>+5</t>
-        </is>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>+5</t>
+          <t>Tuck &amp; Roll</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>HSP</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>-</t>
         </is>
       </c>
       <c r="Q123" t="inlineStr">
         <is>
-          <t>0f5c0eb7-d105-4c6d-9baa-b93ca74ce569</t>
+          <t>c2d21e2d-66e0-46d4-9733-c8f936ca3d82</t>
         </is>
       </c>
       <c r="R123" t="inlineStr">
         <is>
-          <t>a5bb7be7-ae1b-4b04-b3f5-10f712e7f767</t>
-        </is>
-      </c>
-      <c r="S123" t="inlineStr">
-        <is>
-          <t>4510911a-6378-49ee-b18f-8b95ee7d73e1</t>
+          <t>fc7b77a4-f1c5-4ea8-a313-46e23e625a23</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>–– 3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>–– Carnival Sweep</t>
+          <t>Left Flop Punch</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>-53</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>RC</t>
+        </is>
+      </c>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>Continue with the Leg Whip Strings.</t>
         </is>
       </c>
       <c r="Q124" t="inlineStr">
         <is>
-          <t>dd12a5b9-ca44-461c-8fc7-b760b2f8b012</t>
+          <t>511c5803-e5cd-47d4-8b8a-4da8499f5ec6</t>
         </is>
       </c>
       <c r="R124" t="inlineStr">
         <is>
-          <t>cff89a66-2d56-4cfe-9731-6b18d2c42f6b</t>
-        </is>
-      </c>
-      <c r="S124" t="inlineStr">
-        <is>
-          <t>0f5c0eb7-d105-4c6d-9baa-b93ca74ce569</t>
+          <t>2c914bd9-7ae6-48cc-8c08-e4722a912cf2</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Scoot Kick</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>RLX</t>
+          <t>Right Flop Punch</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>-14</t>
+          <t>-2</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>+8</t>
+          <t>+9</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q125" t="inlineStr">
         <is>
-          <t>41acd87c-f316-4882-b1b7-eacda2606ad9</t>
+          <t>4510911a-6378-49ee-b18f-8b95ee7d73e1</t>
         </is>
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>92c0063c-9726-4a89-97f9-3d6526295498</t>
+          <t>4b07173b-e8f3-4dc6-824a-6b3b6476e46c</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>b+3</t>
+          <t>– 4</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Hot Plate</t>
+          <t>– Swirl Kick</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>RLX</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>32</t>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>-28</t>
+          <t>-5</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>-3</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>+5</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q126" t="inlineStr">
         <is>
-          <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
+          <t>0f5c0eb7-d105-4c6d-9baa-b93ca74ce569</t>
         </is>
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>cc9dd02e-62c6-4f80-b851-7431eb9b62e1</t>
+          <t>a5bb7be7-ae1b-4b04-b3f5-10f712e7f767</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>4510911a-6378-49ee-b18f-8b95ee7d73e1</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>– ~D</t>
+          <t>–– 3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>– Hot Plate Cancel</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>RLX</t>
+          <t>–– Carnival Sweep</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>-53</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q127" t="inlineStr">
         <is>
-          <t>5d5bb8d2-5bd6-4ba0-8501-9e44a2e15df9</t>
+          <t>dd12a5b9-ca44-461c-8fc7-b760b2f8b012</t>
         </is>
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>b24c516d-9014-4da2-b916-2a8e8acf8910</t>
+          <t>cff89a66-2d56-4cfe-9731-6b18d2c42f6b</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
+          <t>0f5c0eb7-d105-4c6d-9baa-b93ca74ce569</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>– ~B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>– Hot Plate Cancel</t>
+          <t>Scoot Kick</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>HSP</t>
+          <t>RLX</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>-14</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>+8</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>+8</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>65079a7b-bb56-4efa-9b40-c8f270a11cd4</t>
+          <t>41acd87c-f316-4882-b1b7-eacda2606ad9</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>03a0d7ad-1c8a-4e35-81b5-d05d1bdc8882</t>
-        </is>
-      </c>
-      <c r="S128" t="inlineStr">
-        <is>
-          <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
+          <t>92c0063c-9726-4a89-97f9-3d6526295498</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>– B</t>
+          <t>b+3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>– Handstand Position</t>
+          <t>Hot Plate</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>HSP</t>
+          <t>RLX</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>-28</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>-3</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q129" t="inlineStr">
         <is>
-          <t>5198b605-f40c-4dce-9eb1-1157941a6432</t>
+          <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
         </is>
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>caa0e393-e3a3-42f8-b7cf-544f57c555f1</t>
-        </is>
-      </c>
-      <c r="S129" t="inlineStr">
-        <is>
-          <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
+          <t>cc9dd02e-62c6-4f80-b851-7431eb9b62e1</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>u~3</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>u~4; d~3; d~4</t>
+          <t>– ~D</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Carnival Sweep</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>-14</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>-6</t>
+          <t>– Hot Plate Cancel</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>RLX</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
       <c r="Q130" t="inlineStr">
         <is>
-          <t>2eb8116e-8d2f-41a0-8e3d-fca4561f091c</t>
+          <t>5d5bb8d2-5bd6-4ba0-8501-9e44a2e15df9</t>
         </is>
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>70e07ec3-352b-4cce-8d3b-7e16566602b9</t>
+          <t>b24c516d-9014-4da2-b916-2a8e8acf8910</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>u+3 [~D]</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>u+4 [~D]; d+3 [~D]; d+4 [~D]</t>
+          <t>– ~B</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Slice Kick [RLX]</t>
+          <t>– Hot Plate Cancel</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -7500,153 +7580,128 @@
           <t>HSP</t>
         </is>
       </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>-14</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>7f64d48a-61da-46a7-a8de-d8f58b8776a8</t>
+          <t>65079a7b-bb56-4efa-9b40-c8f270a11cd4</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>ab5704d1-37fb-4bf8-9616-a41a6a9d73a0</t>
+          <t>03a0d7ad-1c8a-4e35-81b5-d05d1bdc8882</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>3~4 [~B]</t>
+          <t>– B</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Slippery Kick [HSP]</t>
+          <t>– Handstand Position</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>RLX</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>-14</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>-6</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>-6</t>
+          <t>HSP</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>10,13</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>LL</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>Continue with the Slippery Kick Series.</t>
+          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>bffcbff7-db7d-4043-ac47-9ee47ec87cc6</t>
+          <t>5198b605-f40c-4dce-9eb1-1157941a6432</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>29558096-0108-4b85-8165-a9e0295a1d84</t>
+          <t>caa0e393-e3a3-42f8-b7cf-544f57c555f1</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>f24e245a-9ee5-4d33-86bc-12a8c9aff669</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>d+3+4</t>
+          <t>u~3</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>u~4; d~3; d~4</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Perch Flop Kick</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>HSP</t>
+          <t>Carnival Sweep</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>16</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -7661,471 +7716,496 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N133" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="P133" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q133" t="inlineStr">
         <is>
-          <t>8b720acf-7ec6-4577-893b-bfb5d6cb43e3</t>
+          <t>2eb8116e-8d2f-41a0-8e3d-fca4561f091c</t>
         </is>
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>eadfcd53-259d-4c25-aed7-e4fe2240079b</t>
+          <t>70e07ec3-352b-4cce-8d3b-7e16566602b9</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>u+3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>u+4; d+3; d+4</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Slice Kick</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>HSP; (~D)RLX</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>-14</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>7f64d48a-61da-46a7-a8de-d8f58b8776a8</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>ab5704d1-37fb-4bf8-9616-a41a6a9d73a0</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>3~4</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Slippery Kick</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>RLX; (~B)HSP</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>-14</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>-6</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>10,13</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>Continue with the Slippery Kick Series.</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>bffcbff7-db7d-4043-ac47-9ee47ec87cc6</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>29558096-0108-4b85-8165-a9e0295a1d84</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>d+3+4</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Perch Flop Kick</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>HSP</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>-13</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>TRUE</t>
+        </is>
+      </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>8b720acf-7ec6-4577-893b-bfb5d6cb43e3</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>eadfcd53-259d-4c25-aed7-e4fe2240079b</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C137" t="inlineStr">
         <is>
           <t>Helicopter</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
+      <c r="D137" t="inlineStr">
         <is>
           <t>HSP</t>
         </is>
       </c>
-      <c r="E134" t="inlineStr">
+      <c r="E137" t="inlineStr">
         <is>
           <t>10 x</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F137" t="inlineStr">
         <is>
           <t>-11 -12</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="G137" t="inlineStr">
         <is>
           <t>-8 KD</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>-8 KD</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr">
+      <c r="I137" t="inlineStr">
         <is>
           <t>12,12</t>
         </is>
       </c>
-      <c r="J134" t="inlineStr">
+      <c r="J137" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr">
+      <c r="K137" t="inlineStr">
         <is>
           <t>sh</t>
         </is>
       </c>
-      <c r="Q134" t="inlineStr">
+      <c r="Q137" t="inlineStr">
         <is>
           <t>8acded53-2f9d-4323-bcaf-0766f532f837</t>
         </is>
       </c>
-      <c r="R134" t="inlineStr">
+      <c r="R137" t="inlineStr">
         <is>
           <t>70d2decc-0404-46a5-9bd6-ce9e83a292e8</t>
         </is>
       </c>
     </row>
-    <row r="135"/>
-    <row r="136">
-      <c r="A136" s="1" t="inlineStr">
+    <row r="138"/>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
         <is>
           <t>Rewinder Arts</t>
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="1" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B137" s="1" t="inlineStr">
+      <c r="B140" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="C137" s="1" t="inlineStr">
+      <c r="C140" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="D137" s="1" t="inlineStr">
+      <c r="D140" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="E137" s="1" t="inlineStr">
+      <c r="E140" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="F137" s="1" t="inlineStr">
+      <c r="F140" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="G137" s="1" t="inlineStr">
+      <c r="G140" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="H137" s="1" t="inlineStr">
+      <c r="H140" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="I137" s="1" t="inlineStr">
+      <c r="I140" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="J137" s="1" t="inlineStr">
+      <c r="J140" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="K137" s="1" t="inlineStr">
+      <c r="K140" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="L137" s="1" t="inlineStr">
+      <c r="L140" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="M137" s="1" t="inlineStr">
+      <c r="M140" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="N137" s="1" t="inlineStr">
+      <c r="N140" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="O137" s="1" t="inlineStr">
+      <c r="O140" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="P137" s="1" t="inlineStr">
+      <c r="P140" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Q137" s="1" t="inlineStr">
+      <c r="Q140" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="R137" s="1" t="inlineStr">
+      <c r="R140" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="S137" s="1" t="inlineStr">
+      <c r="S140" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="T137" s="1" t="inlineStr">
+      <c r="T140" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Moves starting from Rewinder only - SS_1+2_d+1+2</t>
-        </is>
-      </c>
-      <c r="Q138" t="inlineStr">
-        <is>
-          <t>1969a61d-d20b-4b1b-8033-5be235b5db5e</t>
-        </is>
-      </c>
-      <c r="R138" t="inlineStr">
-        <is>
-          <t>797c1da6-3b7a-4181-ba6c-f97f1dda8d7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>1+2</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Spin Slaps</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>11 x</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>x -31</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>x KD</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>x KD</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>12,15</t>
-        </is>
-      </c>
-      <c r="J139" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>hh</t>
-        </is>
-      </c>
-      <c r="O139" t="inlineStr">
-        <is>
-          <t>Side Stepping right away after the move will cancel recovery frames.</t>
-        </is>
-      </c>
-      <c r="Q139" t="inlineStr">
-        <is>
-          <t>56ee9908-67b8-4b86-acec-e94fdc61ccbd</t>
-        </is>
-      </c>
-      <c r="R139" t="inlineStr">
-        <is>
-          <t>fb2443ea-f19d-4232-9488-401e0da62004</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>– ~3</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>– Freak SHOW</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K140" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>JG</t>
-        </is>
-      </c>
-      <c r="P140" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
-      <c r="Q140" t="inlineStr">
-        <is>
-          <t>decc1aa4-e980-405e-a16f-97860935c01f</t>
-        </is>
-      </c>
-      <c r="R140" t="inlineStr">
-        <is>
-          <t>77eb6285-7418-4ba7-ab4f-19d0021b8943</t>
-        </is>
-      </c>
-      <c r="S140" t="inlineStr">
-        <is>
-          <t>56ee9908-67b8-4b86-acec-e94fdc61ccbd</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>– 3</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>– Island Mirage</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>HSP</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>-24</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>m</t>
+          <t>Moves starting from Rewinder only - SS_1+2_d+1+2</t>
         </is>
       </c>
       <c r="Q141" t="inlineStr">
         <is>
-          <t>86e0c0eb-7179-4183-92d4-4e8d042753f2</t>
+          <t>1969a61d-d20b-4b1b-8033-5be235b5db5e</t>
         </is>
       </c>
       <c r="R141" t="inlineStr">
         <is>
-          <t>5fd587ac-ad54-416d-bd30-29dd088a5f08</t>
-        </is>
-      </c>
-      <c r="S141" t="inlineStr">
-        <is>
-          <t>56ee9908-67b8-4b86-acec-e94fdc61ccbd</t>
+          <t>797c1da6-3b7a-4181-ba6c-f97f1dda8d7a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>1+4</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Banda</t>
+          <t>Spin Slaps</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
+          <t>11 x</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>x -31</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>x KD</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>x KD</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>12,15</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>-24</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>hh</t>
+        </is>
+      </c>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>Side Stepping right away after the move will cancel recovery frames.</t>
         </is>
       </c>
       <c r="Q142" t="inlineStr">
         <is>
-          <t>e538d91b-84e9-428e-90f0-cfddcc451c34</t>
+          <t>56ee9908-67b8-4b86-acec-e94fdc61ccbd</t>
         </is>
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>24156857-1b0c-44c2-972e-48a8863b6b0d</t>
+          <t>fb2443ea-f19d-4232-9488-401e0da62004</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>– ~3</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Cruncher</t>
+          <t>– Freak SHOW</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
@@ -8135,64 +8215,69 @@
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>BNc GB</t>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Q143" t="inlineStr">
         <is>
-          <t>b90f4753-8d6d-4a51-9de4-15e59430ea1c</t>
+          <t>decc1aa4-e980-405e-a16f-97860935c01f</t>
         </is>
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>a61fd67a-7ccf-44a9-a03e-58f997dd8ba5</t>
+          <t>77eb6285-7418-4ba7-ab4f-19d0021b8943</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>56ee9908-67b8-4b86-acec-e94fdc61ccbd</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Hot Plate</t>
+          <t>– Island Mirage</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>RLX</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>24</t>
+          <t>HSP</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>-5</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>+9</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
@@ -8202,364 +8287,334 @@
       </c>
       <c r="Q144" t="inlineStr">
         <is>
-          <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
+          <t>86e0c0eb-7179-4183-92d4-4e8d042753f2</t>
         </is>
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>7ce85b52-35c9-48f7-86de-f6d0cbd8c772</t>
+          <t>5fd587ac-ad54-416d-bd30-29dd088a5f08</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>56ee9908-67b8-4b86-acec-e94fdc61ccbd</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>– ~D</t>
+          <t>1+4</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>– Hot Plate Cancel</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>RLX</t>
+          <t>Banda</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-24</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O145" t="inlineStr">
-        <is>
-          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
+          <t>L</t>
         </is>
       </c>
       <c r="Q145" t="inlineStr">
         <is>
-          <t>466a2f97-19a0-4c71-a160-d54dee120154</t>
+          <t>e538d91b-84e9-428e-90f0-cfddcc451c34</t>
         </is>
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>40c9a433-8ac2-46c7-be6f-f7d1c270a106</t>
-        </is>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
+          <t>24156857-1b0c-44c2-972e-48a8863b6b0d</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>– ~B</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>– Hot Plate Cancel</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>HSP</t>
+          <t>Cruncher</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O146" t="inlineStr">
-        <is>
-          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>BNc GB</t>
         </is>
       </c>
       <c r="Q146" t="inlineStr">
         <is>
-          <t>0b29efa5-c707-407b-8c14-df015fa1a042</t>
+          <t>b90f4753-8d6d-4a51-9de4-15e59430ea1c</t>
         </is>
       </c>
       <c r="R146" t="inlineStr">
         <is>
-          <t>14c72d8f-e908-4034-85ed-0df40c791668</t>
-        </is>
-      </c>
-      <c r="S146" t="inlineStr">
-        <is>
-          <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
+          <t>a61fd67a-7ccf-44a9-a03e-58f997dd8ba5</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>– B</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>– Handstand Position</t>
+          <t>Hot Plate</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>HSP</t>
+          <t>RLX</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-5</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>+9</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>+9</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O147" t="inlineStr">
-        <is>
-          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q147" t="inlineStr">
         <is>
-          <t>b8a0c0e0-a2b7-44a5-ab85-7f94be747875</t>
+          <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
         </is>
       </c>
       <c r="R147" t="inlineStr">
         <is>
-          <t>da7e3889-2bfa-4965-9152-a5515386e0b9</t>
-        </is>
-      </c>
-      <c r="S147" t="inlineStr">
-        <is>
-          <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
+          <t>7ce85b52-35c9-48f7-86de-f6d0cbd8c772</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>–– 3+4</t>
+          <t>– ~D</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>–– Instant Perch Flop Kick</t>
+          <t>– Hot Plate Cancel</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>HSP</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>-14</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>RLX</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>-</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
         <is>
-          <t>Only possible if the SS+3 hits or is blocked.</t>
-        </is>
-      </c>
-      <c r="P148" t="inlineStr">
-        <is>
-          <t>TRUE</t>
+          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
       <c r="Q148" t="inlineStr">
         <is>
-          <t>3d796a62-d26d-4bf4-834d-dc8d84196084</t>
+          <t>466a2f97-19a0-4c71-a160-d54dee120154</t>
         </is>
       </c>
       <c r="R148" t="inlineStr">
         <is>
-          <t>922b1b94-f5ed-46d6-9b82-351305cbf0e9</t>
+          <t>40c9a433-8ac2-46c7-be6f-f7d1c270a106</t>
         </is>
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>b8a0c0e0-a2b7-44a5-ab85-7f94be747875</t>
+          <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>3+4</t>
+          <t>– ~B</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Wheel Kick</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>13 x</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>-17 -31</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>x KD</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>x KD</t>
+          <t>– Hot Plate Cancel</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>HSP</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>6,6</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>hm</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
       <c r="Q149" t="inlineStr">
         <is>
-          <t>afb81e0e-130a-49a0-94b7-44302f09074e</t>
+          <t>0b29efa5-c707-407b-8c14-df015fa1a042</t>
         </is>
       </c>
       <c r="R149" t="inlineStr">
         <is>
-          <t>9cc5b23d-9118-44f6-bb48-2b737d8e2ccb</t>
+          <t>14c72d8f-e908-4034-85ed-0df40c791668</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>– 3+4</t>
+          <t>– B</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>– Skull Kick</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>-34</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>– Handstand Position</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>HSP</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N150" t="inlineStr">
-        <is>
-          <t>BN GB</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>Fast B or D inputs will cancel the Hot Plate hit. Input the B after the hit to go into Handstand Position.</t>
         </is>
       </c>
       <c r="Q150" t="inlineStr">
         <is>
-          <t>87d9fba7-d027-4cb2-b63b-2d9f533af40d</t>
+          <t>b8a0c0e0-a2b7-44a5-ab85-7f94be747875</t>
         </is>
       </c>
       <c r="R150" t="inlineStr">
         <is>
-          <t>336b6709-4ed8-47ad-be96-8bdc8b170076</t>
+          <t>da7e3889-2bfa-4965-9152-a5515386e0b9</t>
         </is>
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>afb81e0e-130a-49a0-94b7-44302f09074e</t>
+          <t>9b003da6-b0d5-4fec-9161-81544c2172ef</t>
         </is>
       </c>
     </row>
@@ -8571,12 +8626,17 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>–– Sao Paulo Special</t>
+          <t>–– Instant Perch Flop Kick</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>HSP</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>-11</t>
+          <t>-14</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -8591,168 +8651,183 @@
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>M</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>JG</t>
+        </is>
+      </c>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>Only possible if the SS+3 hits or is blocked.</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="Q151" t="inlineStr">
         <is>
-          <t>88c0fefa-6a80-4d6b-bfe2-40aeb13f31ef</t>
+          <t>3d796a62-d26d-4bf4-834d-dc8d84196084</t>
         </is>
       </c>
       <c r="R151" t="inlineStr">
         <is>
-          <t>f55b7113-123a-421f-a80a-c5c581ff72c1</t>
+          <t>922b1b94-f5ed-46d6-9b82-351305cbf0e9</t>
         </is>
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>87d9fba7-d027-4cb2-b63b-2d9f533af40d</t>
+          <t>b8a0c0e0-a2b7-44a5-ab85-7f94be747875</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>––– uf+3+4 [~B_~D]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>––– Fire Kick [RLX]</t>
+          <t>Wheel Kick</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>13 x</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>-6</t>
+          <t>-17 -31</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x KD</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x KD</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>6,6</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>hm</t>
         </is>
       </c>
       <c r="Q152" t="inlineStr">
         <is>
-          <t>49e65892-9b94-4709-9f04-ee9f63cf6a53</t>
+          <t>afb81e0e-130a-49a0-94b7-44302f09074e</t>
         </is>
       </c>
       <c r="R152" t="inlineStr">
         <is>
-          <t>3b2d9faf-bb6d-467d-bf91-a07d4dfaa390</t>
-        </is>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>88c0fefa-6a80-4d6b-bfe2-40aeb13f31ef</t>
+          <t>9cc5b23d-9118-44f6-bb48-2b737d8e2ccb</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>u+3 [~D]</t>
+          <t>– 3+4</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Skull Kick [RLX]</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
+          <t>– Skull Kick</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>-34</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>-32</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>-30</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
+      <c r="J153" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J153" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>M</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BN GB</t>
         </is>
       </c>
       <c r="Q153" t="inlineStr">
         <is>
-          <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
+          <t>87d9fba7-d027-4cb2-b63b-2d9f533af40d</t>
         </is>
       </c>
       <c r="R153" t="inlineStr">
         <is>
-          <t>1be22aee-cacf-4c5a-990b-1ac7955f4750</t>
+          <t>336b6709-4ed8-47ad-be96-8bdc8b170076</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>afb81e0e-130a-49a0-94b7-44302f09074e</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>– ~3</t>
+          <t>–– 3+4</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>– Freak Show</t>
+          <t>–– Sao Paulo Special</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>-23</t>
+          <t>-11</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -8767,49 +8842,54 @@
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>18</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q154" t="inlineStr">
         <is>
-          <t>259c2d7b-bde2-4a54-a2c8-a2652d2bdcfc</t>
+          <t>88c0fefa-6a80-4d6b-bfe2-40aeb13f31ef</t>
         </is>
       </c>
       <c r="R154" t="inlineStr">
         <is>
-          <t>d0eb9d0e-6194-4d1d-a978-a68f28bbd4b4</t>
+          <t>f55b7113-123a-421f-a80a-c5c581ff72c1</t>
         </is>
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
+          <t>87d9fba7-d027-4cb2-b63b-2d9f533af40d</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>– 3</t>
+          <t>––– uf+3+4</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>– Carnival Sweep</t>
+          <t>––– Fire Kick</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>(~B)RLX; (~D)RLX</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>-56</t>
+          <t>-6</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -8824,116 +8904,116 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q155" t="inlineStr">
         <is>
-          <t>45d6dfb2-ead1-41b0-9302-490de575aa07</t>
+          <t>49e65892-9b94-4709-9f04-ee9f63cf6a53</t>
         </is>
       </c>
       <c r="R155" t="inlineStr">
         <is>
-          <t>e9d07751-7132-4c55-9bf7-8992825cd956</t>
+          <t>3b2d9faf-bb6d-467d-bf91-a07d4dfaa390</t>
         </is>
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
+          <t>88c0fefa-6a80-4d6b-bfe2-40aeb13f31ef</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>– 3+4</t>
+          <t>u+3</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>– Kick Out</t>
+          <t>Skull Kick</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>RLX</t>
+          <t>(~D)RLX</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>25</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>-13</t>
+          <t>-32</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>-30</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>GB</t>
         </is>
       </c>
       <c r="Q156" t="inlineStr">
         <is>
-          <t>b5ed55d8-b877-4585-81ed-04d0c54660d0</t>
+          <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
         </is>
       </c>
       <c r="R156" t="inlineStr">
         <is>
-          <t>bd63768b-2841-49df-9c73-59ce25b1f5dd</t>
-        </is>
-      </c>
-      <c r="S156" t="inlineStr">
-        <is>
-          <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
+          <t>1be22aee-cacf-4c5a-990b-1ac7955f4750</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>4~3 [~B]</t>
+          <t>– ~3</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Leaping Face Kick [HSP]</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>36</t>
+          <t>– Freak Show</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>-12</t>
+          <t>-23</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -8948,74 +9028,69 @@
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>GB</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q157" t="inlineStr">
         <is>
-          <t>9b85822a-6998-47d6-99b9-a7948eda5324</t>
+          <t>259c2d7b-bde2-4a54-a2c8-a2652d2bdcfc</t>
         </is>
       </c>
       <c r="R157" t="inlineStr">
         <is>
-          <t>a9c85d46-aa8c-45c7-9d7b-23f81a08b889</t>
+          <t>d0eb9d0e-6194-4d1d-a978-a68f28bbd4b4</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>4 [~B]</t>
+          <t>– 3</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Swirl Kick [HSP]</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>21</t>
+          <t>– Carnival Sweep</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>-2</t>
+          <t>-56</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>+4</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
@@ -9025,29 +9100,39 @@
       </c>
       <c r="Q158" t="inlineStr">
         <is>
-          <t>da4ad8a1-db1f-4376-8397-632562b526f3</t>
+          <t>45d6dfb2-ead1-41b0-9302-490de575aa07</t>
         </is>
       </c>
       <c r="R158" t="inlineStr">
         <is>
-          <t>4fd67296-1b5c-4c61-a4ed-27ae40c47bcc</t>
+          <t>e9d07751-7132-4c55-9bf7-8992825cd956</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>– 3</t>
+          <t>– 3+4</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>– Carnival Sweep</t>
+          <t>– Kick Out</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>RLX</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>-53</t>
+          <t>-13</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -9062,12 +9147,12 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
@@ -9077,394 +9162,434 @@
       </c>
       <c r="Q159" t="inlineStr">
         <is>
-          <t>0f949d8c-dfc3-4c69-b3cb-55ff2a5828bf</t>
+          <t>b5ed55d8-b877-4585-81ed-04d0c54660d0</t>
         </is>
       </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>5d52d217-0c75-48d4-bbf6-5bf0b4c61027</t>
+          <t>bd63768b-2841-49df-9c73-59ce25b1f5dd</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>da4ad8a1-db1f-4376-8397-632562b526f3</t>
+          <t>0a859ca5-1992-4057-a70c-d71fc915cc3c</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>– 3+4 [~B] [~D]</t>
+          <t>4~3</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>– Front Stinger [HSP] [RLX]</t>
+          <t>Leaping Face Kick</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
+          <t>-12</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>9b85822a-6998-47d6-99b9-a7948eda5324</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>a9c85d46-aa8c-45c7-9d7b-23f81a08b889</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Swirl Kick</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>+4</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>da4ad8a1-db1f-4376-8397-632562b526f3</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>4fd67296-1b5c-4c61-a4ed-27ae40c47bcc</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>– 3</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>– Carnival Sweep</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>-53</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>0f949d8c-dfc3-4c69-b3cb-55ff2a5828bf</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>5d52d217-0c75-48d4-bbf6-5bf0b4c61027</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>da4ad8a1-db1f-4376-8397-632562b526f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>– 3+4</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>– Front Stinger</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>(~B)HSP; (~D)RLX</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="G163" t="inlineStr">
         <is>
           <t>+2</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
+      <c r="H163" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="I160" t="inlineStr">
+      <c r="I163" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
+      <c r="J163" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr">
+      <c r="K163" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="Q160" t="inlineStr">
+      <c r="Q163" t="inlineStr">
         <is>
           <t>7b616e47-8ebb-4154-8160-9d5418a3b56c</t>
         </is>
       </c>
-      <c r="R160" t="inlineStr">
+      <c r="R163" t="inlineStr">
         <is>
           <t>814baccb-ac03-4f45-9007-4ff47eb17944</t>
         </is>
       </c>
-      <c r="S160" t="inlineStr">
+      <c r="S163" t="inlineStr">
         <is>
           <t>da4ad8a1-db1f-4376-8397-632562b526f3</t>
         </is>
       </c>
     </row>
-    <row r="161"/>
-    <row r="162">
-      <c r="A162" s="1" t="inlineStr">
+    <row r="164"/>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
         <is>
           <t>Relaxed Position Arts</t>
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="1" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="B163" s="1" t="inlineStr">
+      <c r="B166" s="1" t="inlineStr">
         <is>
           <t>Alt Commands</t>
         </is>
       </c>
-      <c r="C163" s="1" t="inlineStr">
+      <c r="C166" s="1" t="inlineStr">
         <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="D163" s="1" t="inlineStr">
+      <c r="D166" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="E163" s="1" t="inlineStr">
+      <c r="E166" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="F163" s="1" t="inlineStr">
+      <c r="F166" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="G163" s="1" t="inlineStr">
+      <c r="G166" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="H163" s="1" t="inlineStr">
+      <c r="H166" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="I163" s="1" t="inlineStr">
+      <c r="I166" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="J163" s="1" t="inlineStr">
+      <c r="J166" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="K163" s="1" t="inlineStr">
+      <c r="K166" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="L163" s="1" t="inlineStr">
+      <c r="L166" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="M163" s="1" t="inlineStr">
+      <c r="M166" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="N163" s="1" t="inlineStr">
+      <c r="N166" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="O163" s="1" t="inlineStr">
+      <c r="O166" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="P163" s="1" t="inlineStr">
+      <c r="P166" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="Q163" s="1" t="inlineStr">
+      <c r="Q166" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="R163" s="1" t="inlineStr">
+      <c r="R166" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="S163" s="1" t="inlineStr">
+      <c r="S166" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="T163" s="1" t="inlineStr">
+      <c r="T166" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Moves starting from Relaxed Position only - RLX</t>
-        </is>
-      </c>
-      <c r="Q164" t="inlineStr">
-        <is>
-          <t>fbcf3956-a19f-4979-936b-a082e5c54be6</t>
-        </is>
-      </c>
-      <c r="R164" t="inlineStr">
-        <is>
-          <t>97900bc5-829d-43ca-9962-479ab0e001dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>1+2</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Crying Needle</t>
-        </is>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>-37</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>-21</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>-21</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="O165" t="inlineStr">
-        <is>
-          <t>Hold down or Side Step right away after the move to cancel recovery frames.</t>
-        </is>
-      </c>
-      <c r="Q165" t="inlineStr">
-        <is>
-          <t>522a8f03-06bd-4536-8ac7-bcec87bd1df5</t>
-        </is>
-      </c>
-      <c r="R165" t="inlineStr">
-        <is>
-          <t>0ea6d596-a148-4ec9-814c-17245b2391c3</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>– ~1</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>– Needle Cancel</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="J166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="K166" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="N166" t="inlineStr">
-        <is>
-          <t>RC</t>
-        </is>
-      </c>
-      <c r="Q166" t="inlineStr">
-        <is>
-          <t>5302c69a-79a4-46d9-aeee-219261a791dc</t>
-        </is>
-      </c>
-      <c r="R166" t="inlineStr">
-        <is>
-          <t>c17ad315-8dc2-44b1-a817-f968c975e092</t>
-        </is>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>522a8f03-06bd-4536-8ac7-bcec87bd1df5</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>–– &lt;2</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>–– Hammer Head</t>
-        </is>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>-45</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J167" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K167" t="inlineStr">
-        <is>
-          <t>m</t>
+          <t>Moves starting from Relaxed Position only - RLX</t>
         </is>
       </c>
       <c r="Q167" t="inlineStr">
         <is>
-          <t>bb840600-1410-4ca3-b5b2-177cdb175063</t>
+          <t>fbcf3956-a19f-4979-936b-a082e5c54be6</t>
         </is>
       </c>
       <c r="R167" t="inlineStr">
         <is>
-          <t>d170efb9-e72e-472e-b3ec-5e9647abe966</t>
-        </is>
-      </c>
-      <c r="S167" t="inlineStr">
-        <is>
-          <t>5302c69a-79a4-46d9-aeee-219261a791dc</t>
+          <t>97900bc5-829d-43ca-9962-479ab0e001dc</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>f+1+2</t>
+          <t>1+2</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Headlong Dive</t>
+          <t>Crying Needle</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>-37</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-21</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-21</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
@@ -9472,93 +9597,88 @@
           <t>m</t>
         </is>
       </c>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>Hold down or Side Step right away after the move to cancel recovery frames.</t>
+        </is>
+      </c>
       <c r="Q168" t="inlineStr">
         <is>
-          <t>0afa8b57-c544-4c65-afdb-d72135898321</t>
+          <t>522a8f03-06bd-4536-8ac7-bcec87bd1df5</t>
         </is>
       </c>
       <c r="R168" t="inlineStr">
         <is>
-          <t>4b5b30d6-65e1-4ad9-bce2-9ad97e1ca94f</t>
+          <t>0ea6d596-a148-4ec9-814c-17245b2391c3</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>3,4</t>
+          <t>– ~1</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Rio Delight</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>-15 -1</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>+1 KD</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>+1 KD</t>
+          <t>– Needle Cancel</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>7,28</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>x</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>lm</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>RC</t>
         </is>
       </c>
       <c r="Q169" t="inlineStr">
         <is>
-          <t>642df474-82e5-4e7a-b4bd-6a7d748319e6</t>
+          <t>5302c69a-79a4-46d9-aeee-219261a791dc</t>
         </is>
       </c>
       <c r="R169" t="inlineStr">
         <is>
-          <t>de9e18f3-b06f-4501-a9dd-5e39076b810c</t>
+          <t>c17ad315-8dc2-44b1-a817-f968c975e092</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>522a8f03-06bd-4536-8ac7-bcec87bd1df5</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>3~4</t>
+          <t>–– &lt;2</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Scoop Up Kick</t>
+          <t>–– Hammer Head</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>-24</t>
+          <t>-45</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -9573,471 +9693,552 @@
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="N170" t="inlineStr">
-        <is>
-          <t>JG</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q170" t="inlineStr">
         <is>
-          <t>0d01b647-fe54-4386-8366-bf540afebbdc</t>
+          <t>bb840600-1410-4ca3-b5b2-177cdb175063</t>
         </is>
       </c>
       <c r="R170" t="inlineStr">
         <is>
-          <t>f53dd120-3244-430d-8e35-b1d63c126dd1</t>
+          <t>d170efb9-e72e-472e-b3ec-5e9647abe966</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>5302c69a-79a4-46d9-aeee-219261a791dc</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>3+4 [~B_~3]</t>
+          <t>f+1+2</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Back Handspring [HSP]</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>-8</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>KD</t>
-        </is>
-      </c>
-      <c r="H171" t="inlineStr">
-        <is>
-          <t>KD</t>
+          <t>Headlong Dive</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>M</t>
-        </is>
-      </c>
-      <c r="O171" t="inlineStr">
-        <is>
-          <t>Holding back will cancel the Handspring, tapping 3 will cause the Handspring to hit before going into Handstand Position.</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q171" t="inlineStr">
         <is>
-          <t>1f33d2bc-9841-4057-9510-bae5bf5e46f4</t>
+          <t>0afa8b57-c544-4c65-afdb-d72135898321</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
         <is>
-          <t>60efbe64-fb4d-4a96-906d-1bd1b8484c71</t>
+          <t>4b5b30d6-65e1-4ad9-bce2-9ad97e1ca94f</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>b+3+4</t>
+          <t>3,4</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Rising Feet Lunge</t>
+          <t>Rio Delight</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>-15 -1</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>+1 KD</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>+1 KD</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>7,28</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr">
-        <is>
-          <t>BT</t>
+          <t>lm</t>
         </is>
       </c>
       <c r="Q172" t="inlineStr">
         <is>
-          <t>de459dcb-e7b1-47ef-ba27-674d511033cf</t>
+          <t>642df474-82e5-4e7a-b4bd-6a7d748319e6</t>
         </is>
       </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>1d7286d3-d630-4ef5-abf7-566999d50a64</t>
+          <t>de9e18f3-b06f-4501-a9dd-5e39076b810c</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>4~3</t>
+          <t>3~4</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Flare</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>HSP</t>
+          <t>Scoop Up Kick</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>-30 +3</t>
+          <t>-24</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>+7 +32</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>+7 +32</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>20</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>JG</t>
         </is>
       </c>
       <c r="Q173" t="inlineStr">
         <is>
-          <t>82fe2211-8a53-4732-be5e-580a5ee95203</t>
+          <t>0d01b647-fe54-4386-8366-bf540afebbdc</t>
         </is>
       </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>27cd3819-c33c-4346-889e-0ab9113afe11</t>
+          <t>f53dd120-3244-430d-8e35-b1d63c126dd1</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>4,3+4 [~B_~3]</t>
+          <t>3+4</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Mid Kick - Back Handspring [HSP]</t>
+          <t>Back Handspring</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>35</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>-30</t>
+          <t>-8</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>+7</t>
+          <t>KD</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>10,25</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>mM</t>
-        </is>
-      </c>
-      <c r="O174" t="inlineStr">
-        <is>
-          <t>Hold down or Side Step right away after the move to cancel recovery frames.</t>
+          <t>M</t>
         </is>
       </c>
       <c r="Q174" t="inlineStr">
         <is>
-          <t>3f5cac11-0d1d-42c1-a09e-34f6a66ecdcf</t>
+          <t>1f33d2bc-9841-4057-9510-bae5bf5e46f4</t>
         </is>
       </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>78d3dd69-5c28-4ca9-bfaa-ffa8bd44c236</t>
+          <t>60efbe64-fb4d-4a96-906d-1bd1b8484c71</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3+4~3</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Tag</t>
+          <t>Back Handspring Cancel Into Mid Kick</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>HSP</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q175" t="inlineStr">
         <is>
-          <t>b76844b7-d6c4-487a-b222-0b12c1bc45ff</t>
+          <t>6925d173-ef73-401d-a3d6-8170fb61abd5</t>
         </is>
       </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>e8c50903-ff49-47a3-89c2-6b3321ff8098</t>
-        </is>
-      </c>
-    </row>
-    <row r="176"/>
+          <t>60efbe64-fb4d-4a96-906d-1bd1b8484c71</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>b+3+4</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Rising Feet Lunge</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>BT</t>
+        </is>
+      </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>de459dcb-e7b1-47ef-ba27-674d511033cf</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>1d7286d3-d630-4ef5-abf7-566999d50a64</t>
+        </is>
+      </c>
+    </row>
     <row r="177">
-      <c r="A177" s="1" t="inlineStr">
-        <is>
-          <t>Unblockable Arts</t>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>4~3</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Flare</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>HSP</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>-30 +3</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>+7 +32</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>+7 +32</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>82fe2211-8a53-4732-be5e-580a5ee95203</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>27cd3819-c33c-4346-889e-0ab9113afe11</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="inlineStr">
-        <is>
-          <t>Command</t>
-        </is>
-      </c>
-      <c r="B178" s="1" t="inlineStr">
-        <is>
-          <t>Alt Commands</t>
-        </is>
-      </c>
-      <c r="C178" s="1" t="inlineStr">
-        <is>
-          <t>Move Name</t>
-        </is>
-      </c>
-      <c r="D178" s="1" t="inlineStr">
-        <is>
-          <t>To Stance</t>
-        </is>
-      </c>
-      <c r="E178" s="1" t="inlineStr">
-        <is>
-          <t>Speed</t>
-        </is>
-      </c>
-      <c r="F178" s="1" t="inlineStr">
-        <is>
-          <t>Block Adv</t>
-        </is>
-      </c>
-      <c r="G178" s="1" t="inlineStr">
-        <is>
-          <t>Hit Adv</t>
-        </is>
-      </c>
-      <c r="H178" s="1" t="inlineStr">
-        <is>
-          <t>Counter Hit Adv</t>
-        </is>
-      </c>
-      <c r="I178" s="1" t="inlineStr">
-        <is>
-          <t>Damage</t>
-        </is>
-      </c>
-      <c r="J178" s="1" t="inlineStr">
-        <is>
-          <t>Damage Sum</t>
-        </is>
-      </c>
-      <c r="K178" s="1" t="inlineStr">
-        <is>
-          <t>Hit Range</t>
-        </is>
-      </c>
-      <c r="L178" s="1" t="inlineStr">
-        <is>
-          <t>Throw Type</t>
-        </is>
-      </c>
-      <c r="M178" s="1" t="inlineStr">
-        <is>
-          <t>Throw Escape</t>
-        </is>
-      </c>
-      <c r="N178" s="1" t="inlineStr">
-        <is>
-          <t>Properties</t>
-        </is>
-      </c>
-      <c r="O178" s="1" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="P178" s="1" t="inlineStr">
-        <is>
-          <t>Taggable</t>
-        </is>
-      </c>
-      <c r="Q178" s="1" t="inlineStr">
-        <is>
-          <t>UUID</t>
-        </is>
-      </c>
-      <c r="R178" s="1" t="inlineStr">
-        <is>
-          <t>ML UUID</t>
-        </is>
-      </c>
-      <c r="S178" s="1" t="inlineStr">
-        <is>
-          <t>Parent UUID</t>
-        </is>
-      </c>
-      <c r="T178" s="1" t="inlineStr">
-        <is>
-          <t>Unmatched</t>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>4,3+4</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Mid Kick - Back Handspring</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>(~B)HSP</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>+7</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>10,25</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>mM</t>
+        </is>
+      </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>3f5cac11-0d1d-42c1-a09e-34f6a66ecdcf</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>78d3dd69-5c28-4ca9-bfaa-ffa8bd44c236</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>db+3+4</t>
+          <t>4,3+4~3</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Fruit Picker</t>
+          <t>Mid Kick - Back Handspring Cancel Into Mid Kick</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>HSP</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>x</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>KD</t>
+          <t>x</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>40,40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>[!][!]</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q179" t="inlineStr">
         <is>
-          <t>7adca466-0143-4227-a025-7ff5c051c8d5</t>
+          <t>299aa8c7-44e8-4970-9bf9-34bd859ffdfc</t>
         </is>
       </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>71b7b8ab-5b9f-4a94-8b1c-1414b2989d18</t>
+          <t>78d3dd69-5c28-4ca9-bfaa-ffa8bd44c236</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>– b,b</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>– Cancel</t>
+          <t>Tag</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -10057,17 +10258,12 @@
       </c>
       <c r="Q180" t="inlineStr">
         <is>
-          <t>b3b28c08-1083-41c2-acc3-3cb19e02c822</t>
+          <t>b76844b7-d6c4-487a-b222-0b12c1bc45ff</t>
         </is>
       </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>be655c1e-6671-4778-8c89-b4a0230bab93</t>
-        </is>
-      </c>
-      <c r="S180" t="inlineStr">
-        <is>
-          <t>7adca466-0143-4227-a025-7ff5c051c8d5</t>
+          <t>e8c50903-ff49-47a3-89c2-6b3321ff8098</t>
         </is>
       </c>
     </row>
@@ -10075,7 +10271,7 @@
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
         <is>
-          <t>String Hit Arts</t>
+          <t>Unblockable Arts</t>
         </is>
       </c>
     </row>
@@ -10184,84 +10380,288 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>4~3,4,2,4,4,3+4,3+4,3+4,db+3+4,uf+3+4</t>
+          <t>db+3+4</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Fruit Picker</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>KD</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>KD</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>16,20,28,7,8,9,13,6,6,21,15,20</t>
+          <t>40,40</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>80</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t>mmmhhmmmhmmm</t>
+          <t>!!</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>7adca466-0143-4227-a025-7ff5c051c8d5</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">
         <is>
-          <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
-        </is>
-      </c>
-      <c r="T184" t="inlineStr">
-        <is>
-          <t>ML only</t>
+          <t>71b7b8ab-5b9f-4a94-8b1c-1414b2989d18</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
+          <t>– b,b</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>– Cancel</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>b3b28c08-1083-41c2-acc3-3cb19e02c822</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>be655c1e-6671-4778-8c89-b4a0230bab93</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>7adca466-0143-4227-a025-7ff5c051c8d5</t>
+        </is>
+      </c>
+    </row>
+    <row r="186"/>
+    <row r="187">
+      <c r="A187" s="1" t="inlineStr">
+        <is>
+          <t>String Hit Arts</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>Command</t>
+        </is>
+      </c>
+      <c r="B188" s="1" t="inlineStr">
+        <is>
+          <t>Alt Commands</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="inlineStr">
+        <is>
+          <t>Move Name</t>
+        </is>
+      </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>To Stance</t>
+        </is>
+      </c>
+      <c r="E188" s="1" t="inlineStr">
+        <is>
+          <t>Speed</t>
+        </is>
+      </c>
+      <c r="F188" s="1" t="inlineStr">
+        <is>
+          <t>Block Adv</t>
+        </is>
+      </c>
+      <c r="G188" s="1" t="inlineStr">
+        <is>
+          <t>Hit Adv</t>
+        </is>
+      </c>
+      <c r="H188" s="1" t="inlineStr">
+        <is>
+          <t>Counter Hit Adv</t>
+        </is>
+      </c>
+      <c r="I188" s="1" t="inlineStr">
+        <is>
+          <t>Damage</t>
+        </is>
+      </c>
+      <c r="J188" s="1" t="inlineStr">
+        <is>
+          <t>Damage Sum</t>
+        </is>
+      </c>
+      <c r="K188" s="1" t="inlineStr">
+        <is>
+          <t>Hit Range</t>
+        </is>
+      </c>
+      <c r="L188" s="1" t="inlineStr">
+        <is>
+          <t>Throw Type</t>
+        </is>
+      </c>
+      <c r="M188" s="1" t="inlineStr">
+        <is>
+          <t>Throw Escape</t>
+        </is>
+      </c>
+      <c r="N188" s="1" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="O188" s="1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="P188" s="1" t="inlineStr">
+        <is>
+          <t>Taggable</t>
+        </is>
+      </c>
+      <c r="Q188" s="1" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="R188" s="1" t="inlineStr">
+        <is>
+          <t>ML UUID</t>
+        </is>
+      </c>
+      <c r="S188" s="1" t="inlineStr">
+        <is>
+          <t>Parent UUID</t>
+        </is>
+      </c>
+      <c r="T188" s="1" t="inlineStr">
+        <is>
+          <t>Unmatched</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>4~3,4,2,4,4,3+4,3+4,3+4,db+3+4,uf+3+4</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>16,20,28,7,8,9,13,6,6,21,15,20</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>mmmhhmmmhmmm</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr">
+        <is>
+          <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr">
+        <is>
+          <t>ML only</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
           <t>4~3,4,2,4,3</t>
         </is>
       </c>
-      <c r="I185" t="inlineStr">
+      <c r="I190" t="inlineStr">
         <is>
           <t>16,20,28,7,8,12</t>
         </is>
       </c>
-      <c r="J185" t="inlineStr">
+      <c r="J190" t="inlineStr">
         <is>
           <t>91</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr">
+      <c r="K190" t="inlineStr">
         <is>
           <t>mmmhhL</t>
         </is>
       </c>
-      <c r="R185" t="inlineStr">
+      <c r="R190" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
         </is>
       </c>
-      <c r="T185" t="inlineStr">
+      <c r="T190" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
+    <row r="191">
+      <c r="A191" t="inlineStr">
         <is>
           <t>– Leg Whip Series</t>
         </is>
       </c>
-      <c r="R186" t="inlineStr">
+      <c r="R191" t="inlineStr">
         <is>
           <t>b321b883-5528-4383-9e3a-01d93e60f6ab</t>
         </is>
       </c>
-      <c r="S186" t="inlineStr">
+      <c r="S191" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
         </is>
       </c>
-      <c r="T186" t="inlineStr">
+      <c r="T191" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>

--- a/sources/eddy_step6b.xlsx
+++ b/sources/eddy_step6b.xlsx
@@ -733,6 +733,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>69fcfb4c-f026-4bd0-86cd-aab7af8a4f9d</t>
@@ -780,6 +785,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>72845d08-c01c-4c2e-b9bb-eb6bf7061e42</t>
@@ -825,6 +835,11 @@
       <c r="M8" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>89b9a62a-0e17-41f7-9bcd-95c83f81b48a</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -10602,6 +10617,11 @@
           <t>mmmhhmmmhmmm</t>
         </is>
       </c>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
+        </is>
+      </c>
       <c r="R189" t="inlineStr">
         <is>
           <t>75dc99c7-8cb7-47d7-b907-7045f1e2dcd1</t>
@@ -10634,6 +10654,11 @@
           <t>mmmhhL</t>
         </is>
       </c>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
+        </is>
+      </c>
       <c r="R190" t="inlineStr">
         <is>
           <t>daff2cc0-5de1-450f-b06c-c4e7db7f803b</t>
@@ -10649,6 +10674,11 @@
       <c r="A191" t="inlineStr">
         <is>
           <t>– Leg Whip Series</t>
+        </is>
+      </c>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>b321b883-5528-4383-9e3a-01d93e60f6ab</t>
         </is>
       </c>
       <c r="R191" t="inlineStr">
